--- a/LubanConfig/MiniTemplate/Datas/__beans__.xlsx
+++ b/LubanConfig/MiniTemplate/Datas/__beans__.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\悠手好闲\铁头工作室\方块项目设计案\《冲王》数值python\LubanConfig\MiniTemplate\Datas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\悠手好闲\铁头工作室\方块项目设计案\《冲王》数值_cursor\LubanConfig\MiniTemplate\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="48">
   <si>
     <t>##var</t>
   </si>
@@ -139,6 +139,162 @@
   </si>
   <si>
     <t>技能描述</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>Wave</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Data</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>enemy</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>_group_list</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>time</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>_between_waves</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>float</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>list,EnemyGroup</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>Enemy</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Group</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>enemy</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>_id</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>enemy</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>_count</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>current</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>_level</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>time_between_groups</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>time_between_enemies</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>reset</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>_hp</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>int</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -230,7 +386,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -247,6 +403,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -526,7 +685,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:P10"/>
+  <dimension ref="A1:P18"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="4" width="20.625" customWidth="1"/>
@@ -692,6 +851,76 @@
         <v>31</v>
       </c>
     </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="B11" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="J11" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="L11" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="J12" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="L12" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="B13" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="J13" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="L13" s="2" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="J14" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="L14" s="2" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="J15" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="L15" s="2" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="J16" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="L16" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="17" spans="10:12" x14ac:dyDescent="0.2">
+      <c r="J17" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="L17" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="18" spans="10:12" x14ac:dyDescent="0.2">
+      <c r="J18" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="L18" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="J1:P1"/>

--- a/LubanConfig/MiniTemplate/Datas/__beans__.xlsx
+++ b/LubanConfig/MiniTemplate/Datas/__beans__.xlsx
@@ -14,12 +14,12 @@
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="144525"/>
+  <calcPr calcId="162913"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="54">
   <si>
     <t>##var</t>
   </si>
@@ -295,6 +295,30 @@
   </si>
   <si>
     <t>int</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>资源数据</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>类型</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>数值</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>浮动范围</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>float</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>string</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -402,10 +426,10 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -685,7 +709,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:P18"/>
+  <dimension ref="A1:P21"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="4" width="20.625" customWidth="1"/>
@@ -723,15 +747,15 @@
       <c r="I1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="5" t="s">
+      <c r="J1" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="5"/>
-      <c r="L1" s="5"/>
-      <c r="M1" s="5"/>
-      <c r="N1" s="5"/>
-      <c r="O1" s="5"/>
-      <c r="P1" s="5"/>
+      <c r="K1" s="6"/>
+      <c r="L1" s="6"/>
+      <c r="M1" s="6"/>
+      <c r="N1" s="6"/>
+      <c r="O1" s="6"/>
+      <c r="P1" s="6"/>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
@@ -905,20 +929,47 @@
         <v>38</v>
       </c>
     </row>
-    <row r="17" spans="10:12" x14ac:dyDescent="0.2">
-      <c r="J17" s="6" t="s">
+    <row r="17" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="J17" s="5" t="s">
         <v>45</v>
       </c>
       <c r="L17" s="2" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="18" spans="10:12" x14ac:dyDescent="0.2">
-      <c r="J18" s="6" t="s">
+    <row r="18" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="J18" s="5" t="s">
         <v>44</v>
       </c>
       <c r="L18" s="2" t="s">
         <v>38</v>
+      </c>
+    </row>
+    <row r="19" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B19" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="J19" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="L19" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="20" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="J20" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="L20" s="2" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="21" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="J21" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="L21" s="2" t="s">
+        <v>52</v>
       </c>
     </row>
   </sheetData>
